--- a/data/sample-too-thick-playbook.xlsx
+++ b/data/sample-too-thick-playbook.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="128">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="138">
   <si>
     <t>Fill in the playbook title and the label ID it belongs to.</t>
   </si>
@@ -73,7 +73,10 @@
     <t>Product looks dry or freezer-burned</t>
   </si>
   <si>
-    <t>Evidence the assistant should collect during diagnosis.</t>
+    <t>Evidence the assistant should collect during diagnosis. "action_id" is optional and should match an ID in Admin -&gt; Actions.</t>
+  </si>
+  <si>
+    <t>action_id</t>
   </si>
   <si>
     <t>type</t>
@@ -88,6 +91,9 @@
     <t>Machine model</t>
   </si>
   <si>
+    <t>identify_machine_model</t>
+  </si>
+  <si>
     <t>observation</t>
   </si>
   <si>
@@ -100,6 +106,9 @@
     <t>Photo of product dispense showing thickness</t>
   </si>
   <si>
+    <t>photo_dispense_front</t>
+  </si>
+  <si>
     <t>photo</t>
   </si>
   <si>
@@ -109,6 +118,9 @@
     <t>Hopper temperature reading (normal range -8°C to -4°C; below this can cause thick product)</t>
   </si>
   <si>
+    <t>read_hopper_temp</t>
+  </si>
+  <si>
     <t>reading</t>
   </si>
   <si>
@@ -118,6 +130,9 @@
     <t>Cylinder temperature reading if available</t>
   </si>
   <si>
+    <t>read_cylinder_temp</t>
+  </si>
+  <si>
     <t>no</t>
   </si>
   <si>
@@ -127,18 +142,27 @@
     <t>Current mix-to-water ratio being used</t>
   </si>
   <si>
+    <t>check_mix_ratio</t>
+  </si>
+  <si>
     <t>last_defrost</t>
   </si>
   <si>
     <t>When the machine was last defrosted</t>
   </si>
   <si>
+    <t>report_last_defrost</t>
+  </si>
+  <si>
     <t>scraper_condition</t>
   </si>
   <si>
     <t>Condition of scraper blades</t>
   </si>
   <si>
+    <t>inspect_scraper_blades</t>
+  </si>
+  <si>
     <t>action</t>
   </si>
   <si>
@@ -148,6 +172,9 @@
     <t>Air overrun / aeration level setting</t>
   </si>
   <si>
+    <t>check_overrun_setting</t>
+  </si>
+  <si>
     <t>Possible root causes the assistant will try to narrow down.</t>
   </si>
   <si>
@@ -208,7 +235,7 @@
     <t>low</t>
   </si>
   <si>
-    <t>Diagnostic questions the assistant can ask the user.</t>
+    <t>Diagnostic questions the assistant can ask the user. "action_id" is optional and should match an ID in Admin -&gt; Actions.</t>
   </si>
   <si>
     <t>question</t>
@@ -266,6 +293,9 @@
   </si>
   <si>
     <t>If other causes ruled out</t>
+  </si>
+  <si>
+    <t>count_pulls_hour</t>
   </si>
   <si>
     <t>ask_overrun</t>
@@ -905,24 +935,26 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D10"/>
+  <dimension ref="A1:E10"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="25" customWidth="1"/>
     <col min="2" max="2" width="50" customWidth="1"/>
-    <col min="3" max="3" width="18" customWidth="1"/>
-    <col min="4" max="4" width="12" customWidth="1"/>
+    <col min="3" max="3" width="25" customWidth="1"/>
+    <col min="4" max="4" width="18" customWidth="1"/>
+    <col min="5" max="5" width="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="40" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" ht="40" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>18</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
       <c r="D1" s="1"/>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E1" s="1"/>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>6</v>
       </c>
@@ -935,122 +967,149 @@
       <c r="D2" s="2" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E2" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D3" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+        <v>25</v>
+      </c>
+      <c r="E3" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
+        <v>27</v>
+      </c>
+      <c r="B4" t="s">
+        <v>28</v>
+      </c>
+      <c r="C4" t="s">
+        <v>29</v>
+      </c>
+      <c r="D4" t="s">
+        <v>30</v>
+      </c>
+      <c r="E4" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>31</v>
+      </c>
+      <c r="B5" t="s">
+        <v>32</v>
+      </c>
+      <c r="C5" t="s">
+        <v>33</v>
+      </c>
+      <c r="D5" t="s">
+        <v>34</v>
+      </c>
+      <c r="E5" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>35</v>
+      </c>
+      <c r="B6" t="s">
+        <v>36</v>
+      </c>
+      <c r="C6" t="s">
+        <v>37</v>
+      </c>
+      <c r="D6" t="s">
+        <v>34</v>
+      </c>
+      <c r="E6" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>39</v>
+      </c>
+      <c r="B7" t="s">
+        <v>40</v>
+      </c>
+      <c r="C7" t="s">
+        <v>41</v>
+      </c>
+      <c r="D7" t="s">
         <v>25</v>
       </c>
-      <c r="B4" t="s">
+      <c r="E7" t="s">
         <v>26</v>
       </c>
-      <c r="C4" t="s">
-        <v>27</v>
-      </c>
-      <c r="D4" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>28</v>
-      </c>
-      <c r="B5" t="s">
-        <v>29</v>
-      </c>
-      <c r="C5" t="s">
-        <v>30</v>
-      </c>
-      <c r="D5" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>31</v>
-      </c>
-      <c r="B6" t="s">
-        <v>32</v>
-      </c>
-      <c r="C6" t="s">
-        <v>30</v>
-      </c>
-      <c r="D6" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>42</v>
+      </c>
+      <c r="B8" t="s">
+        <v>43</v>
+      </c>
+      <c r="C8" t="s">
+        <v>44</v>
+      </c>
+      <c r="D8" t="s">
+        <v>25</v>
+      </c>
+      <c r="E8" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>45</v>
+      </c>
+      <c r="B9" t="s">
+        <v>46</v>
+      </c>
+      <c r="C9" t="s">
+        <v>47</v>
+      </c>
+      <c r="D9" t="s">
+        <v>48</v>
+      </c>
+      <c r="E9" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>49</v>
+      </c>
+      <c r="B10" t="s">
+        <v>50</v>
+      </c>
+      <c r="C10" t="s">
+        <v>51</v>
+      </c>
+      <c r="D10" t="s">
         <v>34</v>
       </c>
-      <c r="B7" t="s">
-        <v>35</v>
-      </c>
-      <c r="C7" t="s">
-        <v>23</v>
-      </c>
-      <c r="D7" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>36</v>
-      </c>
-      <c r="B8" t="s">
-        <v>37</v>
-      </c>
-      <c r="C8" t="s">
-        <v>23</v>
-      </c>
-      <c r="D8" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
+      <c r="E10" t="s">
         <v>38</v>
-      </c>
-      <c r="B9" t="s">
-        <v>39</v>
-      </c>
-      <c r="C9" t="s">
-        <v>40</v>
-      </c>
-      <c r="D9" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>41</v>
-      </c>
-      <c r="B10" t="s">
-        <v>42</v>
-      </c>
-      <c r="C10" t="s">
-        <v>30</v>
-      </c>
-      <c r="D10" t="s">
-        <v>33</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A1:E1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
@@ -1070,7 +1129,7 @@
   <sheetData>
     <row r="1" ht="40" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>43</v>
+        <v>52</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -1081,97 +1140,97 @@
         <v>6</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>44</v>
+        <v>53</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>46</v>
+        <v>55</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>47</v>
+        <v>56</v>
       </c>
       <c r="B3" t="s">
-        <v>48</v>
+        <v>57</v>
       </c>
       <c r="C3" t="s">
-        <v>49</v>
+        <v>58</v>
       </c>
       <c r="D3" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="B4" t="s">
-        <v>51</v>
+        <v>60</v>
       </c>
       <c r="C4" t="s">
-        <v>49</v>
+        <v>58</v>
       </c>
       <c r="D4" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>52</v>
+        <v>61</v>
       </c>
       <c r="B5" t="s">
-        <v>53</v>
+        <v>62</v>
       </c>
       <c r="C5" t="s">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="D5" t="s">
-        <v>41</v>
+        <v>49</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>55</v>
+        <v>64</v>
       </c>
       <c r="B6" t="s">
-        <v>56</v>
+        <v>65</v>
       </c>
       <c r="C6" t="s">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="D6" t="s">
-        <v>57</v>
+        <v>66</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>58</v>
+        <v>67</v>
       </c>
       <c r="B7" t="s">
-        <v>59</v>
+        <v>68</v>
       </c>
       <c r="C7" t="s">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="D7" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>60</v>
+        <v>69</v>
       </c>
       <c r="B8" t="s">
-        <v>61</v>
+        <v>70</v>
       </c>
       <c r="C8" t="s">
-        <v>62</v>
+        <v>71</v>
       </c>
       <c r="D8" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
     </row>
   </sheetData>
@@ -1185,110 +1244,130 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D7"/>
+  <dimension ref="A1:E7"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="25" customWidth="1"/>
     <col min="2" max="2" width="50" customWidth="1"/>
     <col min="3" max="3" width="40" customWidth="1"/>
     <col min="4" max="4" width="30" customWidth="1"/>
+    <col min="5" max="5" width="25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="40" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" ht="40" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>63</v>
+        <v>72</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
       <c r="D1" s="1"/>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E1" s="1"/>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>64</v>
+        <v>73</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>65</v>
+        <v>74</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+        <v>75</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>67</v>
+        <v>76</v>
       </c>
       <c r="B3" t="s">
-        <v>68</v>
+        <v>77</v>
       </c>
       <c r="C3" t="s">
-        <v>69</v>
+        <v>78</v>
       </c>
       <c r="D3" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+        <v>79</v>
+      </c>
+      <c r="E3" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>71</v>
+        <v>80</v>
       </c>
       <c r="B4" t="s">
-        <v>72</v>
+        <v>81</v>
       </c>
       <c r="C4" t="s">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="D4" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+        <v>83</v>
+      </c>
+      <c r="E4" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="B5" t="s">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="C5" t="s">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="D5" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+        <v>87</v>
+      </c>
+      <c r="E5" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="B6" t="s">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="C6" t="s">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="D6" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+        <v>91</v>
+      </c>
+      <c r="E6" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="B7" t="s">
-        <v>84</v>
+        <v>94</v>
       </c>
       <c r="C7" t="s">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="D7" t="s">
-        <v>86</v>
+        <v>96</v>
+      </c>
+      <c r="E7" t="s">
+        <v>51</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A1:E1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
@@ -1306,56 +1385,56 @@
   <sheetData>
     <row r="1" ht="40" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>87</v>
+        <v>97</v>
       </c>
       <c r="B1" s="1"/>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>88</v>
+        <v>98</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>89</v>
+        <v>99</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="B3" t="s">
-        <v>91</v>
+        <v>101</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="B4" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="B5" t="s">
-        <v>95</v>
+        <v>105</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>96</v>
+        <v>106</v>
       </c>
       <c r="B6" t="s">
-        <v>97</v>
+        <v>107</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>98</v>
+        <v>108</v>
       </c>
       <c r="B7" t="s">
-        <v>99</v>
+        <v>109</v>
       </c>
     </row>
   </sheetData>
@@ -1379,7 +1458,7 @@
   <sheetData>
     <row r="1" ht="40" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -1390,97 +1469,97 @@
         <v>1</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>101</v>
+        <v>111</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>102</v>
+        <v>112</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>103</v>
+        <v>113</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="B3" t="s">
-        <v>105</v>
+        <v>115</v>
       </c>
       <c r="C3" t="s">
-        <v>106</v>
+        <v>116</v>
       </c>
       <c r="D3" t="s">
-        <v>107</v>
+        <v>117</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>108</v>
+        <v>118</v>
       </c>
       <c r="B4" t="s">
-        <v>109</v>
+        <v>119</v>
       </c>
       <c r="C4" t="s">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="D4" t="s">
-        <v>111</v>
+        <v>121</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>112</v>
+        <v>122</v>
       </c>
       <c r="B5" t="s">
-        <v>113</v>
+        <v>123</v>
       </c>
       <c r="C5" t="s">
-        <v>114</v>
+        <v>124</v>
       </c>
       <c r="D5" t="s">
-        <v>115</v>
+        <v>125</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>116</v>
+        <v>126</v>
       </c>
       <c r="B6" t="s">
-        <v>117</v>
+        <v>127</v>
       </c>
       <c r="C6" t="s">
-        <v>118</v>
+        <v>128</v>
       </c>
       <c r="D6" t="s">
-        <v>119</v>
+        <v>129</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="B7" t="s">
-        <v>121</v>
+        <v>131</v>
       </c>
       <c r="C7" t="s">
-        <v>122</v>
+        <v>132</v>
       </c>
       <c r="D7" t="s">
-        <v>123</v>
+        <v>133</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>124</v>
+        <v>134</v>
       </c>
       <c r="B8" t="s">
-        <v>125</v>
+        <v>135</v>
       </c>
       <c r="C8" t="s">
-        <v>126</v>
+        <v>136</v>
       </c>
       <c r="D8" t="s">
-        <v>127</v>
+        <v>137</v>
       </c>
     </row>
   </sheetData>
